--- a/artfynd/A 72312-2021 artfynd.xlsx
+++ b/artfynd/A 72312-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 72312-2021 artfynd.xlsx
+++ b/artfynd/A 72312-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102126354</v>
+        <v>102126346</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>405658.815657653</v>
+        <v>405637</v>
       </c>
       <c r="R2" t="n">
-        <v>6722491.397103755</v>
+        <v>6722365</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102126353</v>
+        <v>102126357</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>405731.0209111726</v>
+        <v>405725</v>
       </c>
       <c r="R3" t="n">
-        <v>6722375.59620268</v>
+        <v>6722519</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102126349</v>
+        <v>102126352</v>
       </c>
       <c r="B4" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>405665.4356772389</v>
+        <v>405632</v>
       </c>
       <c r="R4" t="n">
-        <v>6722200.064721838</v>
+        <v>6722451</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102126368</v>
+        <v>102126353</v>
       </c>
       <c r="B5" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>405632.9706087291</v>
+        <v>405731</v>
       </c>
       <c r="R5" t="n">
-        <v>6722218.592790226</v>
+        <v>6722375</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102126358</v>
+        <v>102126354</v>
       </c>
       <c r="B6" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>405725.451984083</v>
+        <v>405659</v>
       </c>
       <c r="R6" t="n">
-        <v>6722519.598860225</v>
+        <v>6722492</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102126367</v>
+        <v>102126356</v>
       </c>
       <c r="B7" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405632.9706087291</v>
+        <v>405697</v>
       </c>
       <c r="R7" t="n">
-        <v>6722218.592790226</v>
+        <v>6722324</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1228,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,19 +1257,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102126362</v>
+        <v>102126361</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>405664.9273321446</v>
+        <v>405662</v>
       </c>
       <c r="R8" t="n">
-        <v>6722330.685038574</v>
+        <v>6722206</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1325,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,19 +1354,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102126361</v>
+        <v>102126362</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>405662.1498232255</v>
+        <v>405665</v>
       </c>
       <c r="R9" t="n">
-        <v>6722206.043052237</v>
+        <v>6722331</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,19 +1422,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,37 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>102126347</v>
+        <v>102126364</v>
       </c>
       <c r="B10" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>405636.3027081462</v>
+        <v>405680</v>
       </c>
       <c r="R10" t="n">
-        <v>6722364.332483619</v>
+        <v>6722430</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,19 +1519,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,19 +1548,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>102126352</v>
+        <v>102126366</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1723,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>405632.1926762662</v>
+        <v>405688</v>
       </c>
       <c r="R11" t="n">
-        <v>6722451.344601326</v>
+        <v>6722262</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,19 +1616,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>102126346</v>
+        <v>102126347</v>
       </c>
       <c r="B12" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>405636.3027081462</v>
+        <v>405637</v>
       </c>
       <c r="R12" t="n">
-        <v>6722364.332483619</v>
+        <v>6722365</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,19 +1713,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>102126363</v>
+        <v>102126350</v>
       </c>
       <c r="B13" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405702.3474435023</v>
+        <v>405684</v>
       </c>
       <c r="R13" t="n">
-        <v>6722201.060823541</v>
+        <v>6722190</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,19 +1810,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>102126364</v>
+        <v>102126351</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405679.3344285021</v>
+        <v>405714</v>
       </c>
       <c r="R14" t="n">
-        <v>6722429.977733964</v>
+        <v>6722550</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2092,19 +1907,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,15 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>102126365</v>
+        <v>102126355</v>
       </c>
       <c r="B15" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2171,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>405712.1382649672</v>
+        <v>405621</v>
       </c>
       <c r="R15" t="n">
-        <v>6722199.331103051</v>
+        <v>6722279</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2204,19 +2004,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,15 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>102126348</v>
+        <v>102126363</v>
       </c>
       <c r="B16" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2259,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>405636.3027081462</v>
+        <v>405702</v>
       </c>
       <c r="R16" t="n">
-        <v>6722364.332483619</v>
+        <v>6722201</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2316,19 +2101,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,15 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>102126355</v>
+        <v>102126365</v>
       </c>
       <c r="B17" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>405620.3017719851</v>
+        <v>405712</v>
       </c>
       <c r="R17" t="n">
-        <v>6722279.318984537</v>
+        <v>6722200</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,19 +2198,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,15 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>102126369</v>
+        <v>102126348</v>
       </c>
       <c r="B18" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2507,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>405752.7288556609</v>
+        <v>405637</v>
       </c>
       <c r="R18" t="n">
-        <v>6722246.87710282</v>
+        <v>6722365</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2540,19 +2295,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,15 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>102126366</v>
+        <v>102126358</v>
       </c>
       <c r="B19" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>405688.7073148465</v>
+        <v>405725</v>
       </c>
       <c r="R19" t="n">
-        <v>6722262.303467209</v>
+        <v>6722519</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2652,19 +2392,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2694,12 +2424,7 @@
         <v>102126359</v>
       </c>
       <c r="B20" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>405682.7997803976</v>
+        <v>405683</v>
       </c>
       <c r="R20" t="n">
-        <v>6722337.090212055</v>
+        <v>6722337</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2764,19 +2489,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,15 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>102126357</v>
+        <v>102126367</v>
       </c>
       <c r="B21" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2819,21 +2529,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>405725.451984083</v>
+        <v>405633</v>
       </c>
       <c r="R21" t="n">
-        <v>6722519.598860225</v>
+        <v>6722218</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2876,19 +2586,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,15 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>102126356</v>
+        <v>102126369</v>
       </c>
       <c r="B22" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2931,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>405696.7173858022</v>
+        <v>405753</v>
       </c>
       <c r="R22" t="n">
-        <v>6722323.95939136</v>
+        <v>6722247</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2988,19 +2683,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,15 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>102126351</v>
+        <v>102126349</v>
       </c>
       <c r="B23" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3043,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>405713.9638430785</v>
+        <v>405665</v>
       </c>
       <c r="R23" t="n">
-        <v>6722550.33997012</v>
+        <v>6722200</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3100,19 +2780,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,15 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>102126350</v>
+        <v>102126368</v>
       </c>
       <c r="B24" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3155,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>405683.3756190182</v>
+        <v>405633</v>
       </c>
       <c r="R24" t="n">
-        <v>6722190.2649813</v>
+        <v>6722218</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3212,19 +2877,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 72312-2021 artfynd.xlsx
+++ b/artfynd/A 72312-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102126346</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102126357</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102126352</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102126353</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102126354</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102126356</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102126361</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102126362</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102126364</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102126366</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102126347</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102126350</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102126351</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102126355</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102126363</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102126365</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102126348</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102126358</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102126359</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102126367</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102126369</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102126349</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,8 +3018,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102126368</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>